--- a/AAII_Financials/Quarterly/FGPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FGPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>FGPR</t>
   </si>
@@ -656,467 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>524600</v>
+      </c>
+      <c r="F8" s="3">
         <v>641400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>355200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>343600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>560800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>669800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>364100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>340500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>515800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>609900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>371000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>341900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>587300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>683900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>413300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>387600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>647500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1079400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>394500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>335100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>564700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>553600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>300900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>281600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>412100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>510800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>293200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>279100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>479600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>573400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>352300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>347500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>515800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>755200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>155900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>233100</v>
+      </c>
+      <c r="F9" s="3">
         <v>291000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>160000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>152700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>271600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>322400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>168800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>152300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>243500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>281600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>176600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>153200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>295500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>351700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>217900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>209100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>365700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>996500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>223700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>177300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>300900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>273800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>140800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>127700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>178600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>240900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>137300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>139100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>252700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>315000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>207200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>210700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>294800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>488700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>291400</v>
+      </c>
+      <c r="F10" s="3">
         <v>350400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>195200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>190900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>289200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>347400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>195300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>188100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>272300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>328300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>194400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>188700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>291800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>332200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>195400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>178500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>281800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>82900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>170800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>157800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>263800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>279800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>160100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>153900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>233500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>269900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>155900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>140000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>226900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>258400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>145100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>136800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>221000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>266500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1178,10 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1284,14 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,58 +1394,64 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>400</v>
+      </c>
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>4200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-1600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>127300</v>
+      </c>
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1421,69 +1460,75 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-4900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>118900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1200</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>37400</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>27600</v>
+      </c>
+      <c r="F15" s="3">
         <v>26500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>25200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>25400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>24300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>24300</v>
       </c>
       <c r="I15" s="3">
         <v>24300</v>
@@ -1492,85 +1537,91 @@
         <v>24300</v>
       </c>
       <c r="K15" s="3">
+        <v>24300</v>
+      </c>
+      <c r="L15" s="3">
+        <v>24300</v>
+      </c>
+      <c r="M15" s="3">
         <v>25300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>24400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>24400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>23900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>23800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>23100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>22600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>24600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>23100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>42200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>20300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>21500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>21300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>21200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>21400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>21100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>20400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>19800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>19200</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>19600</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>20600</v>
       </c>
       <c r="AF15" s="3">
         <v>19600</v>
       </c>
       <c r="AG15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="AI15" s="3">
         <v>19000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>25200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>340800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>464100</v>
+      </c>
+      <c r="F17" s="3">
         <v>503900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>352100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>347100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>472700</v>
       </c>
-      <c r="H17" s="3">
-        <v>539900</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>414900</v>
+      </c>
+      <c r="K17" s="3">
         <v>485600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>336600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>438900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>489100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>364600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>344100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>489600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>561600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>393500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>382000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>555300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>932100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>382100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>329700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>590300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>440200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>293100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>297900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>381600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>414500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>292600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>306000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>414800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>484700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>365800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>523200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>464500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>715100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>60500</v>
+      </c>
+      <c r="F18" s="3">
         <v>137500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>88100</v>
       </c>
-      <c r="H18" s="3">
-        <v>129900</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>254900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-121500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>76900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>120800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>97800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>122400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>19800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>5600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>92200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>147300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>12400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>5400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-25600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>113400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>7800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>30500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>96300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-26900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>64800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>88700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-13500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-175700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>51300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,37 +1915,39 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-800</v>
       </c>
       <c r="M20" s="3">
         <v>-1300</v>
@@ -1889,489 +1956,519 @@
         <v>-800</v>
       </c>
       <c r="O20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>4400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>3500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>-100</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>88800</v>
+      </c>
+      <c r="F21" s="3">
         <v>164500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>28900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>22900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>113300</v>
       </c>
-      <c r="H21" s="3">
-        <v>154600</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>279600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-96300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>29100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>103500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>146100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>32200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>22400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>122400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>146000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>42900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>30600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>115400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>193800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>36900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>27000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>138200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>29300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>50800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>116200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>19700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-7300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>85700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>108400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>5500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-150900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>74600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>64000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>32400</v>
+      </c>
+      <c r="F22" s="3">
         <v>33200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>26700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>25900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>28100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>27900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>26100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>25000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>24700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>24400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>24200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>25200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>24300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>23200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>25000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>25600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>24000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>50500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>25400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>24600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>42200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>52600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>54200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>54000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>45700</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>47500</v>
       </c>
       <c r="AC22" s="3">
         <v>45700</v>
       </c>
       <c r="AD22" s="3">
+        <v>47500</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>45700</v>
+      </c>
+      <c r="AF22" s="3">
         <v>44700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>44200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>44900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>43900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>44600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>40500</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F23" s="3">
         <v>103400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-27200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-26800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>59900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>100100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-148200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-21200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>53400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>96900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-17700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-29500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>73400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>99400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-19600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>68400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>101100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-8800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-19100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-67200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>64300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-46400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-70500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-15300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>48900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-45200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-71600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>20900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>43900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-57400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-220800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
+        <v>300</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>400</v>
       </c>
       <c r="H24" s="3">
         <v>400</v>
       </c>
       <c r="I24" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
       <c r="N24" s="3">
+        <v>300</v>
+      </c>
+      <c r="O24" s="3">
+        <v>200</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>200</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>28200</v>
+      </c>
+      <c r="F26" s="3">
         <v>103100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-27400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-27300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>59500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>99700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-148300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-21200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>53100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>96600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-17900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-29600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>73000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>98900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-19800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>68100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>100500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-8900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-19200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-67400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>64000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-46500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-70600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>48800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-45700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-71700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>20800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>43900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-57500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-217800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12200</v>
+        <v>124400</v>
       </c>
       <c r="E27" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="F27" s="3">
+        <v>48400</v>
+      </c>
+      <c r="G27" s="3">
         <v>-6200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-42600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>6100</v>
       </c>
-      <c r="H27" s="3">
-        <v>11700</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>48400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-91500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-36800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-63800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>49800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>6100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>13500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-35400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>7300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>9300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-20700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-34700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-74100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>62600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-45600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-69300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>47700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-44900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-70300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>20300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>42900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-56400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-213500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +3011,14 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,37 +3231,43 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>700</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>800</v>
       </c>
       <c r="M32" s="3">
         <v>1300</v>
@@ -3137,177 +3276,189 @@
         <v>800</v>
       </c>
       <c r="O32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-4400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>100</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F33" s="3">
         <v>102200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-26900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-26700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>59100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>98800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-146700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-21900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>52800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>95800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-17600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-30500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>72400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>98100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-35400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>7300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>9300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-20700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-34700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-74100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>62600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-45600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-69300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>47700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-44900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-70300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>20300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>42900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-56400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-213500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F35" s="3">
         <v>102200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-26900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-26700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>59100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>98800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-146700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-21900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>52800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>95800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-17600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-30500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>72400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>98100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-35400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>7300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>9300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-20700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-34700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-74100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>62600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-45600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-69300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>47700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-44900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-70300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>20300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>42900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-56400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-213500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3870,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>73400</v>
+      </c>
+      <c r="F41" s="3">
         <v>88400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>28400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>96900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>109300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>39400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>37000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>113500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>62900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>128400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>66000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>126200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>93500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>112600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>44200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>147500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>217900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>188400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>157400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>270500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>211300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>217400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>202600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>238000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>177500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>13700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>29800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>11100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>45400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>40600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>63200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>119300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,424 +4086,454 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>178700</v>
+      </c>
+      <c r="F43" s="3">
         <v>238600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>133600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>127500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>183100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>254700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>139700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>120600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>178200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>226900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>150500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>159400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>199000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>233600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>158700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>150400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>219300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>253900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>163500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>131600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>170500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>206300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>119500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>101400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>143000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>182400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>123800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>107600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>157200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>203200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>136200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>126100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>202700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>256000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>79500</v>
+      </c>
+      <c r="F44" s="3">
         <v>85500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>91900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>87800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>86100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>104600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>101100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>96000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>91300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>100300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>105800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>98100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>97800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>113400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>120100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>115200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>100600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>118100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>131300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>88400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>69700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>90500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>79000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>72700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>65200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>78500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>85000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>80500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>78400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>89800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>106600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>83700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>85100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>110100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F45" s="3">
         <v>26200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>35000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>17000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>29800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>40900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>50400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>20600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>33700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>49000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>49500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>41100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>43800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>66300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>104600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>85000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>125400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>152600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>200500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>128600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>85500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>182000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>137000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>131700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>188500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>47800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>50600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>42300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>25500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>36600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>34000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>34900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>44100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>93600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>291900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>371100</v>
+      </c>
+      <c r="F46" s="3">
         <v>453500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>299300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>342700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>408300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>439600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>338800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>375200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>376800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>515300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>382600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>435900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>445300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>537000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>427600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>498100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>663100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>713000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>652600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>619000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>537100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>696200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>538100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>543800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>574200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>322400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>289200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>241400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>306600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>370200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>339900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>363900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>341400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>473800</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4370,273 +4579,291 @@
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3">
         <v>400</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X47" s="3">
         <v>19800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB47" s="3">
         <v>5300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>8800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>11300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>13800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>16200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>27500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>27600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>27600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>27500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>36400</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>626700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>644500</v>
+      </c>
+      <c r="F48" s="3">
         <v>634700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>639400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>679500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>650800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>641700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>650400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>677400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>678600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>677000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>671800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>697500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>679500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>671800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>675900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>707500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>704700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>702400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>707200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>704600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>712900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>723200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>732200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>739800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>732000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>729400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>728700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>596700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>603900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>584300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>566100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>557700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>637700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>646300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>356400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>358100</v>
+      </c>
+      <c r="F49" s="3">
         <v>359900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>361800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>363600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>365500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>367400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>369300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>369200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>371500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>373900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>361300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>363600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>365800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>365400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>362900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>354700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>350300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>352300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>354300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>347700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>344500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>346600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>348800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>351200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>351200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>353400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>355700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>355800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>357100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>361000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>364900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>367000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>481400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>489200</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +5076,124 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>94100</v>
+      </c>
+      <c r="F52" s="3">
         <v>95200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>78000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>30900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>71100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>70300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>55200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>37000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>60800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>54700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>56400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>34300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>64700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>66800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>71200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>47400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>54400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>52300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>62500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>38600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>50200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>53100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>33800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>28000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>54200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>54700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>55900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>52900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>34800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>44900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>45300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>47100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>41300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1364800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1467900</v>
+      </c>
+      <c r="F54" s="3">
         <v>1543300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1378500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1416700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1495700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1519000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1413700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1458800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1487700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1621000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1472100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1531400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1555400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1641000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1537600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1608100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1772500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1820100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1776600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1729600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1644700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1819000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1652800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1668200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1720300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1471200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1443300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1263000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1330000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1388100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1343800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1363300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1532600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1687100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5490,670 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F57" s="3">
         <v>74500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>55300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>31100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>49100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>77700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>46400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>33800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>47700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>67900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>45900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>35100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>49800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>87400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>60800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>57600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>81000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>113300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>80200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>47900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>54300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>79200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>44600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>33900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>37000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>46100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>44400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>33400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>41400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>63600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>59700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>46800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>52500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>82100</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>104400</v>
+      </c>
+      <c r="F58" s="3">
         <v>79600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>17700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>680700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>669500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>20000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>23000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>33700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>26700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>28000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>27600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>33400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>26900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>26700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>17400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>8400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>8300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>8200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>7900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>9100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>9000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>509300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>866300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>866100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>363600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>522800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>512900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>736800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>62000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>140000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>90000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>93200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>104000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>427200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>171800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>110300</v>
+      </c>
+      <c r="F59" s="3">
         <v>116400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>117600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>128100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>179000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>199500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>248300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>103500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>103200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>126400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>131200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>111500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>112600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>146300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>233100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>237900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>245600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>289700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>302000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>263900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>197700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>212400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>208000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>189900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>202200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>186000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>219700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>138200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>160500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>147300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>186000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>139600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>158900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>140500</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>312400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>351700</v>
+      </c>
+      <c r="F60" s="3">
         <v>350800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>289000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>914500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>947800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>363300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>357200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>242800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>228400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>299700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>248700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>259300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>241900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>335900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>311400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>303800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>334900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>411300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>390200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>320900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>261100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>800900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1119000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1089900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>602800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>754900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>777100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>908400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>263900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>350900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>335600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>279600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>315300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>649800</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2130400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2129600</v>
+      </c>
+      <c r="F61" s="3">
         <v>2127000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2126800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1518100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1490200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2136000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2136900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2155700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2144600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2140400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2139500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2161400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2143500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2144600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1451700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1475300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1475600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1475400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1474700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1472900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1472700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1680900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1679100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1679900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2166300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1744200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1735900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1457000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2084500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2083000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2081200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>2078600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>1995600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>1811600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>54600</v>
+      </c>
+      <c r="F62" s="3">
         <v>55900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>44700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>13300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>42800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>41300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>28100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>10000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>28700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>25600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>26400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>9500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>32100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>33600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>80300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>65400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>74300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>84100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>108100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>107500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>100400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>99900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>100800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>106700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>108100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>116800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>121700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>36500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>35900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>37500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>38700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>39500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>34200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>35400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2494500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2535900</v>
+      </c>
+      <c r="F66" s="3">
         <v>2533700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2460600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2445800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2480800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2540600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2522200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2408400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2401700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2465600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2414600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2430200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2417500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2514100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1835000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1837000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1877900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1963500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1965300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1893400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1825900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2964300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2890400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2868200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2869400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2608100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2626500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2394200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2377500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2464300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2448100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>2391100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>2340800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>2492400</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6562,67 +6897,73 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>579800</v>
       </c>
-      <c r="R70" s="3">
+      <c r="T70" s="3">
         <v>580000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="U70" s="3">
         <v>580400</v>
       </c>
-      <c r="T70" s="3">
+      <c r="V70" s="3">
         <v>579900</v>
       </c>
-      <c r="U70" s="3">
+      <c r="W70" s="3">
         <v>578900</v>
       </c>
-      <c r="V70" s="3">
+      <c r="X70" s="3">
         <v>579200</v>
       </c>
-      <c r="W70" s="3">
+      <c r="Y70" s="3">
         <v>580000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Z70" s="3">
         <v>-71100</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="AA70" s="3">
         <v>-71700</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AB70" s="3">
         <v>-71300</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AC70" s="3">
         <v>-70600</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AD70" s="3">
         <v>-70400</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AE70" s="3">
         <v>-70900</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AF70" s="3">
         <v>-70500</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AG70" s="3">
         <v>-69800</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AH70" s="3">
         <v>-70000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AI70" s="3">
         <v>-70400</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AJ70" s="3">
         <v>-69800</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AK70" s="3">
         <v>-67600</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AL70" s="3">
         <v>-67600</v>
       </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +7066,14 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6769,11 +7116,11 @@
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S72" s="3">
         <v>0</v>
@@ -6829,8 +7176,14 @@
       <c r="AJ72" s="3">
         <v>0</v>
       </c>
+      <c r="AK72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1051100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-990200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-911900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-1001700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-949800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-906600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-942400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-1027500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-871900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-837000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-767900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-864000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-821000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-785200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-795000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-877300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-808900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-685800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-723300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-767600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-742900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-761200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-1074200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-1165800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-1128800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-1078400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-1066500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-1112300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-1060800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-977700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-1006200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-1033900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>-958000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>-740700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>-737700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F81" s="3">
         <v>102200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-26900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-26700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>59100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>98800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-146700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-21900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>52800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>95800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-17600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-30500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>72400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>98100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-35400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>7300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>9300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-20700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-34700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-74100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>62600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-45600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-69300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>47700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-44900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-70300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>20300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>42900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-56400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-213500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7995,120 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>24300</v>
+        <v>17500</v>
       </c>
       <c r="E83" s="3">
         <v>24300</v>
       </c>
       <c r="F83" s="3">
+        <v>24300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>24300</v>
+      </c>
+      <c r="H83" s="3">
         <v>15000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>25300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>24400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>24400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>15400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>23800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>23100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>22600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>16500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>23100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>21900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>22600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>24600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>23100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>42200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>20300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>21500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>21300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>21200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>21400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>21100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>20400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>19800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>19200</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>19600</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>20600</v>
       </c>
       <c r="AF83" s="3">
         <v>19600</v>
       </c>
       <c r="AG83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>19600</v>
+      </c>
+      <c r="AI83" s="3">
         <v>19000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>25200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>118500</v>
+      </c>
+      <c r="F89" s="3">
         <v>40700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-8500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>19800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>118000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>32900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-34300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>69600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>75400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>119400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-18900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>69100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>86000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>124000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-66800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>32300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>76700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>51500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-15300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>103500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>58500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>55900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>14500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>115200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>7100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-55700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>125900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-37500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-17600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>114600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-44200</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8805,120 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-22500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-21700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-11800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-26500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-19700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-22000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-22100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-23800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-23500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-18700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-28900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-22200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-25600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-30400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-20200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-20400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-10100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>34700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-19500</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>84700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-36300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-23400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-23300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +9131,124 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-22000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-21300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-11000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-25600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-19100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-25100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-21500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-39400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-23100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-18500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-33000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-34800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-35000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-28100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-48700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-29600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-14000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-14800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-14100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>4900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-27600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-34700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-42200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-34200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>65500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,16 +9285,18 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
+        <v>107000</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
@@ -8843,32 +9310,32 @@
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>100000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>50000</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-50000</v>
+      <c r="R96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -8877,13 +9344,13 @@
         <v>-50000</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-50000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
-        <v>0</v>
+        <v>-50000</v>
       </c>
       <c r="X96" s="3">
         <v>0</v>
@@ -8913,10 +9380,10 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
-        <v>-9800</v>
+        <v>0</v>
       </c>
       <c r="AH96" s="3">
-        <v>-9800</v>
+        <v>0</v>
       </c>
       <c r="AI96" s="3">
         <v>-9800</v>
@@ -8924,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>-9800</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>-9800</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9721,124 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-106400</v>
+      </c>
+      <c r="F100" s="3">
         <v>41300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-38700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-21200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-22500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-22000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-17100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-18100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-119400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-17600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-18600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-17900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-72100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-67700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-19100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-85200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-68300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-30400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-147400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>235100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>4300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>46300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>42100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-79000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>49100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>48400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-149600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9384,11 +9881,11 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -9444,108 +9941,120 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="F102" s="3">
         <v>60000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-68500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-12400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>69900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-8200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-76500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>50500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-65500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>62400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-60600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>32700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-19100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>68500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-103400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-70400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>29500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-82300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-113100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>59100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-103600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>27000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>14900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>305100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>18800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-34400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>4800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-22500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-56100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>109800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>7100</v>
       </c>
     </row>
